--- a/PWN/栈溢出/系统调用x86-64.xlsx
+++ b/PWN/栈溢出/系统调用x86-64.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EF63D2-DFC3-41D3-A510-6841EF093D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643232DC-D183-45C2-AB6F-4BE651A82C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,9 +40,6 @@
     <t>%rdx</t>
   </si>
   <si>
-    <t>%rcx</t>
-  </si>
-  <si>
     <t>%r8</t>
   </si>
   <si>
@@ -3044,13 +3041,17 @@
   </si>
   <si>
     <t>const struct iovcc *rvec</t>
+  </si>
+  <si>
+    <t>%r10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3082,6 +3083,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3105,7 +3115,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3117,6 +3127,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3449,14 +3462,14 @@
       <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="28" x14ac:dyDescent="0.25">
@@ -3464,19 +3477,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -3487,19 +3500,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -3510,19 +3523,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -3533,13 +3546,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -3552,16 +3565,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -3573,16 +3586,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -3594,16 +3607,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -3615,19 +3628,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -3638,19 +3651,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -3661,28 +3674,28 @@
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -3690,19 +3703,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -3713,16 +3726,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -3734,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -3753,22 +3766,22 @@
         <v>13</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -3778,22 +3791,22 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="G18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -3803,13 +3816,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -3822,19 +3835,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -3845,22 +3858,22 @@
         <v>17</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -3870,22 +3883,22 @@
         <v>18</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -3895,19 +3908,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -3918,19 +3931,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -3941,16 +3954,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -3962,13 +3975,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -3981,25 +3994,25 @@
         <v>23</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="I27" s="3"/>
     </row>
@@ -4008,10 +4021,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -4025,25 +4038,25 @@
         <v>25</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="I29" s="3"/>
     </row>
@@ -4052,19 +4065,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="D30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="F30" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -4075,19 +4088,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -4098,19 +4111,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -4121,19 +4134,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -4144,19 +4157,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
@@ -4167,19 +4180,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -4190,13 +4203,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -4209,16 +4222,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -4230,10 +4243,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -4247,16 +4260,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -4268,16 +4281,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
@@ -4289,13 +4302,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -4308,19 +4321,19 @@
         <v>38</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
@@ -4331,10 +4344,10 @@
         <v>39</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -4348,22 +4361,22 @@
         <v>40</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="G44" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -4373,19 +4386,19 @@
         <v>41</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
@@ -4396,19 +4409,19 @@
         <v>42</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="F46" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4419,19 +4432,19 @@
         <v>43</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
@@ -4442,28 +4455,28 @@
         <v>44</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="F48" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G48" s="3" t="s">
+      <c r="H48" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="I48" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -4471,28 +4484,28 @@
         <v>45</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="F49" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -4500,19 +4513,19 @@
         <v>46</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="F50" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -4523,19 +4536,19 @@
         <v>47</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
@@ -4546,16 +4559,16 @@
         <v>48</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -4567,19 +4580,19 @@
         <v>49</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="F53" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -4590,16 +4603,16 @@
         <v>50</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -4611,19 +4624,19 @@
         <v>51</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
@@ -4634,19 +4647,19 @@
         <v>52</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E56" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
@@ -4657,22 +4670,22 @@
         <v>53</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -4682,25 +4695,25 @@
         <v>54</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="I58" s="3"/>
     </row>
@@ -4709,25 +4722,25 @@
         <v>55</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="I59" s="3"/>
     </row>
@@ -4736,22 +4749,22 @@
         <v>56</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="F60" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="G60" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -4761,10 +4774,10 @@
         <v>57</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -4778,10 +4791,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -4795,19 +4808,19 @@
         <v>59</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
@@ -4818,13 +4831,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -4837,22 +4850,22 @@
         <v>61</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="F65" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="G65" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -4862,16 +4875,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="E66" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -4883,13 +4896,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -4902,19 +4915,19 @@
         <v>64</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E68" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
@@ -4925,19 +4938,19 @@
         <v>65</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
@@ -4948,22 +4961,22 @@
         <v>66</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E70" s="3" t="s">
+      <c r="F70" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G70" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
@@ -4973,13 +4986,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>258</v>
-      </c>
       <c r="D71" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -4992,16 +5005,16 @@
         <v>68</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -5013,22 +5026,22 @@
         <v>69</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="F73" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="G73" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
@@ -5038,25 +5051,25 @@
         <v>70</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G74" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="H74" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I74" s="3"/>
     </row>
@@ -5065,19 +5078,19 @@
         <v>71</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F75" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
@@ -5088,19 +5101,19 @@
         <v>72</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="D76" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E76" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F76" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
@@ -5111,16 +5124,16 @@
         <v>73</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>276</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
@@ -5132,13 +5145,13 @@
         <v>74</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>278</v>
-      </c>
       <c r="D78" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -5151,13 +5164,13 @@
         <v>75</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>280</v>
-      </c>
       <c r="D79" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -5170,16 +5183,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>284</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -5191,16 +5204,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -5212,19 +5225,19 @@
         <v>78</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="D82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E82" s="3" t="s">
+      <c r="F82" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
@@ -5235,16 +5248,16 @@
         <v>79</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -5256,13 +5269,13 @@
         <v>80</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>296</v>
-      </c>
       <c r="D84" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -5275,13 +5288,13 @@
         <v>81</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>298</v>
-      </c>
       <c r="D85" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -5294,16 +5307,16 @@
         <v>82</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="D86" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
@@ -5315,16 +5328,16 @@
         <v>83</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="D87" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="E87" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -5336,13 +5349,13 @@
         <v>84</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>307</v>
-      </c>
       <c r="D88" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -5355,16 +5368,16 @@
         <v>85</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="D89" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
@@ -5376,16 +5389,16 @@
         <v>86</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>311</v>
-      </c>
       <c r="D90" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
@@ -5397,13 +5410,13 @@
         <v>87</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>313</v>
-      </c>
       <c r="D91" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -5416,16 +5429,16 @@
         <v>88</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="D92" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
@@ -5437,19 +5450,19 @@
         <v>89</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="D93" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
@@ -5460,16 +5473,16 @@
         <v>90</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="D94" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>321</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
@@ -5481,16 +5494,16 @@
         <v>91</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>323</v>
-      </c>
       <c r="D95" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
@@ -5502,19 +5515,19 @@
         <v>92</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="D96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
@@ -5525,19 +5538,19 @@
         <v>93</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="D97" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E97" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F97" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
@@ -5548,19 +5561,19 @@
         <v>94</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>331</v>
-      </c>
       <c r="D98" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E98" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F98" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
@@ -5571,13 +5584,13 @@
         <v>95</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>334</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -5590,16 +5603,16 @@
         <v>96</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="D100" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="E100" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -5611,16 +5624,16 @@
         <v>97</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="E101" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -5632,16 +5645,16 @@
         <v>98</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="D102" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="E102" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
@@ -5653,13 +5666,13 @@
         <v>99</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>348</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
@@ -5672,13 +5685,13 @@
         <v>100</v>
       </c>
       <c r="B104" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>350</v>
-      </c>
       <c r="D104" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
@@ -5691,22 +5704,22 @@
         <v>101</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="D105" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="E105" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="F105" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
@@ -5716,10 +5729,10 @@
         <v>102</v>
       </c>
       <c r="B106" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -5733,19 +5746,19 @@
         <v>103</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="D107" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F107" s="3" t="s">
         <v>359</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>360</v>
       </c>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -5756,10 +5769,10 @@
         <v>104</v>
       </c>
       <c r="B108" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -5773,13 +5786,13 @@
         <v>105</v>
       </c>
       <c r="B109" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="D109" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
@@ -5792,13 +5805,13 @@
         <v>106</v>
       </c>
       <c r="B110" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="D110" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>368</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
@@ -5811,10 +5824,10 @@
         <v>107</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -5828,10 +5841,10 @@
         <v>108</v>
       </c>
       <c r="B112" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>372</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -5845,16 +5858,16 @@
         <v>109</v>
       </c>
       <c r="B113" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="D113" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E113" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
@@ -5866,10 +5879,10 @@
         <v>110</v>
       </c>
       <c r="B114" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -5883,10 +5896,10 @@
         <v>111</v>
       </c>
       <c r="B115" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -5900,10 +5913,10 @@
         <v>112</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>381</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -5917,16 +5930,16 @@
         <v>113</v>
       </c>
       <c r="B117" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="D117" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="E117" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>385</v>
       </c>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
@@ -5938,16 +5951,16 @@
         <v>114</v>
       </c>
       <c r="B118" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="D118" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="E118" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
@@ -5959,16 +5972,16 @@
         <v>115</v>
       </c>
       <c r="B119" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="D119" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="E119" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
@@ -5980,16 +5993,16 @@
         <v>116</v>
       </c>
       <c r="B120" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C120" s="3" t="s">
-        <v>395</v>
-      </c>
       <c r="D120" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="E120" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
@@ -6001,19 +6014,19 @@
         <v>117</v>
       </c>
       <c r="B121" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="D121" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="E121" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="F121" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="3"/>
@@ -6024,19 +6037,19 @@
         <v>118</v>
       </c>
       <c r="B122" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C122" s="3" t="s">
-        <v>402</v>
-      </c>
       <c r="D122" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="E122" s="3" t="s">
+      <c r="F122" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
@@ -6047,19 +6060,19 @@
         <v>119</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="D123" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="E123" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="F123" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>406</v>
       </c>
       <c r="G123" s="3"/>
       <c r="H123" s="3"/>
@@ -6070,19 +6083,19 @@
         <v>120</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="D124" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="F124" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="G124" s="3"/>
       <c r="H124" s="3"/>
@@ -6093,13 +6106,13 @@
         <v>121</v>
       </c>
       <c r="B125" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C125" s="3" t="s">
-        <v>413</v>
-      </c>
       <c r="D125" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
@@ -6112,13 +6125,13 @@
         <v>122</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C126" s="3" t="s">
-        <v>415</v>
-      </c>
       <c r="D126" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
@@ -6131,13 +6144,13 @@
         <v>123</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="D127" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>418</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
@@ -6150,13 +6163,13 @@
         <v>124</v>
       </c>
       <c r="B128" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C128" s="3" t="s">
-        <v>420</v>
-      </c>
       <c r="D128" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
@@ -6169,16 +6182,16 @@
         <v>125</v>
       </c>
       <c r="B129" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="E129" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>424</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
@@ -6190,16 +6203,16 @@
         <v>126</v>
       </c>
       <c r="B130" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="D130" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E130" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
@@ -6211,16 +6224,16 @@
         <v>127</v>
       </c>
       <c r="B131" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="D131" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>430</v>
-      </c>
       <c r="E131" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
@@ -6232,22 +6245,22 @@
         <v>128</v>
       </c>
       <c r="B132" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="D132" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D132" s="3" t="s">
+      <c r="E132" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="E132" s="3" t="s">
+      <c r="F132" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="F132" s="3" t="s">
-        <v>435</v>
-      </c>
       <c r="G132" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
@@ -6257,19 +6270,19 @@
         <v>129</v>
       </c>
       <c r="B133" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C133" s="3" t="s">
-        <v>437</v>
-      </c>
       <c r="D133" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="3"/>
@@ -6280,16 +6293,16 @@
         <v>130</v>
       </c>
       <c r="B134" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="C134" s="3" t="s">
+      <c r="D134" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D134" s="3" t="s">
-        <v>440</v>
-      </c>
       <c r="E134" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
@@ -6301,16 +6314,16 @@
         <v>131</v>
       </c>
       <c r="B135" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="D135" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="D135" s="3" t="s">
+      <c r="E135" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
@@ -6322,16 +6335,16 @@
         <v>132</v>
       </c>
       <c r="B136" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="D136" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="E136" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="E136" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3"/>
@@ -6343,19 +6356,19 @@
         <v>133</v>
       </c>
       <c r="B137" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="D137" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F137" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F137" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="G137" s="3"/>
       <c r="H137" s="3"/>
@@ -6366,13 +6379,13 @@
         <v>134</v>
       </c>
       <c r="B138" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="D138" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>454</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
@@ -6385,13 +6398,13 @@
         <v>135</v>
       </c>
       <c r="B139" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="D139" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
@@ -6404,16 +6417,16 @@
         <v>136</v>
       </c>
       <c r="B140" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="D140" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="E140" s="3" t="s">
         <v>459</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>460</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
@@ -6425,16 +6438,16 @@
         <v>137</v>
       </c>
       <c r="B141" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="D141" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="3"/>
@@ -6446,16 +6459,16 @@
         <v>138</v>
       </c>
       <c r="B142" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C142" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="D142" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3"/>
@@ -6467,19 +6480,19 @@
         <v>139</v>
       </c>
       <c r="B143" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="D143" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="E143" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="E143" s="3" t="s">
+      <c r="F143" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="G143" s="3"/>
       <c r="H143" s="3"/>
@@ -6490,16 +6503,16 @@
         <v>140</v>
       </c>
       <c r="B144" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C144" s="3" t="s">
-        <v>472</v>
-      </c>
       <c r="D144" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
@@ -6511,19 +6524,19 @@
         <v>141</v>
       </c>
       <c r="B145" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C145" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="D145" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F145" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="G145" s="3"/>
       <c r="H145" s="3"/>
@@ -6534,16 +6547,16 @@
         <v>142</v>
       </c>
       <c r="B146" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="D146" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E146" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3"/>
@@ -6555,16 +6568,16 @@
         <v>143</v>
       </c>
       <c r="B147" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C147" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C147" s="3" t="s">
-        <v>480</v>
-      </c>
       <c r="D147" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
@@ -6576,19 +6589,19 @@
         <v>144</v>
       </c>
       <c r="B148" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C148" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="D148" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E148" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="F148" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G148" s="3"/>
       <c r="H148" s="3"/>
@@ -6599,13 +6612,13 @@
         <v>145</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C149" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="C149" s="3" t="s">
-        <v>485</v>
-      </c>
       <c r="D149" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
@@ -6618,13 +6631,13 @@
         <v>146</v>
       </c>
       <c r="B150" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C150" s="3" t="s">
-        <v>487</v>
-      </c>
       <c r="D150" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
@@ -6637,13 +6650,13 @@
         <v>147</v>
       </c>
       <c r="B151" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C151" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="D151" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
@@ -6656,16 +6669,16 @@
         <v>148</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C152" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="D152" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E152" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
@@ -6677,16 +6690,16 @@
         <v>149</v>
       </c>
       <c r="B153" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C153" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C153" s="3" t="s">
-        <v>494</v>
-      </c>
       <c r="D153" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E153" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
@@ -6698,16 +6711,16 @@
         <v>150</v>
       </c>
       <c r="B154" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C154" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C154" s="3" t="s">
-        <v>496</v>
-      </c>
       <c r="D154" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E154" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
@@ -6719,13 +6732,13 @@
         <v>151</v>
       </c>
       <c r="B155" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C155" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="C155" s="3" t="s">
-        <v>498</v>
-      </c>
       <c r="D155" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
@@ -6738,10 +6751,10 @@
         <v>152</v>
       </c>
       <c r="B156" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C156" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -6755,10 +6768,10 @@
         <v>153</v>
       </c>
       <c r="B157" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C157" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -6772,19 +6785,19 @@
         <v>154</v>
       </c>
       <c r="B158" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C158" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="D158" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="E158" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="E158" s="3" t="s">
+      <c r="F158" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="G158" s="3"/>
       <c r="H158" s="3"/>
@@ -6795,16 +6808,16 @@
         <v>155</v>
       </c>
       <c r="B159" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C159" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="D159" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="E159" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>511</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
@@ -6816,13 +6829,13 @@
         <v>156</v>
       </c>
       <c r="B160" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="D160" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
@@ -6835,25 +6848,25 @@
         <v>157</v>
       </c>
       <c r="B161" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C161" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="D161" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F161" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="D161" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="F161" s="3" t="s">
+      <c r="G161" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="G161" s="3" t="s">
+      <c r="H161" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="H161" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="I161" s="3"/>
     </row>
@@ -6862,19 +6875,19 @@
         <v>158</v>
       </c>
       <c r="B162" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C162" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="C162" s="3" t="s">
+      <c r="D162" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="D162" s="3" t="s">
+      <c r="E162" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="E162" s="3" t="s">
+      <c r="F162" s="3" t="s">
         <v>523</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>524</v>
       </c>
       <c r="G162" s="3"/>
       <c r="H162" s="3"/>
@@ -6885,13 +6898,13 @@
         <v>159</v>
       </c>
       <c r="B163" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C163" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="D163" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>527</v>
       </c>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
@@ -6904,16 +6917,16 @@
         <v>160</v>
       </c>
       <c r="B164" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C164" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="C164" s="3" t="s">
-        <v>529</v>
-      </c>
       <c r="D164" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E164" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
@@ -6925,13 +6938,13 @@
         <v>161</v>
       </c>
       <c r="B165" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C165" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="C165" s="3" t="s">
-        <v>531</v>
-      </c>
       <c r="D165" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
@@ -6944,10 +6957,10 @@
         <v>162</v>
       </c>
       <c r="B166" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C166" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>533</v>
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -6961,13 +6974,13 @@
         <v>163</v>
       </c>
       <c r="B167" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="D167" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
@@ -6980,16 +6993,16 @@
         <v>164</v>
       </c>
       <c r="B168" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C168" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="C168" s="3" t="s">
-        <v>538</v>
-      </c>
       <c r="D168" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E168" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
@@ -7001,25 +7014,25 @@
         <v>165</v>
       </c>
       <c r="B169" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C169" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="D169" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D169" s="3" t="s">
+      <c r="E169" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="E169" s="3" t="s">
+      <c r="F169" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="F169" s="3" t="s">
+      <c r="G169" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H169" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H169" s="3" t="s">
-        <v>544</v>
       </c>
       <c r="I169" s="3"/>
     </row>
@@ -7028,16 +7041,16 @@
         <v>166</v>
       </c>
       <c r="B170" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C170" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="C170" s="3" t="s">
+      <c r="D170" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="D170" s="3" t="s">
-        <v>547</v>
-      </c>
       <c r="E170" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
@@ -7049,16 +7062,16 @@
         <v>167</v>
       </c>
       <c r="B171" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C171" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="C171" s="3" t="s">
+      <c r="D171" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="D171" s="3" t="s">
+      <c r="E171" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>551</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
@@ -7070,13 +7083,13 @@
         <v>168</v>
       </c>
       <c r="B172" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="C172" s="3" t="s">
-        <v>553</v>
-      </c>
       <c r="D172" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
@@ -7089,22 +7102,22 @@
         <v>169</v>
       </c>
       <c r="B173" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="C173" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="C173" s="3" t="s">
+      <c r="D173" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="D173" s="3" t="s">
+      <c r="E173" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E173" s="3" t="s">
+      <c r="F173" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G173" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="H173" s="3"/>
       <c r="I173" s="3"/>
@@ -7114,16 +7127,16 @@
         <v>170</v>
       </c>
       <c r="B174" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C174" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="C174" s="3" t="s">
+      <c r="D174" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="D174" s="3" t="s">
-        <v>561</v>
-      </c>
       <c r="E174" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3"/>
@@ -7135,16 +7148,16 @@
         <v>171</v>
       </c>
       <c r="B175" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C175" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>563</v>
-      </c>
       <c r="D175" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3"/>
@@ -7156,16 +7169,16 @@
         <v>172</v>
       </c>
       <c r="B176" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="C176" s="3" t="s">
+      <c r="D176" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="D176" s="3" t="s">
+      <c r="E176" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="E176" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3"/>
@@ -7177,19 +7190,19 @@
         <v>173</v>
       </c>
       <c r="B177" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C177" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="C177" s="3" t="s">
+      <c r="D177" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="D177" s="3" t="s">
+      <c r="E177" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="E177" s="3" t="s">
+      <c r="F177" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>572</v>
       </c>
       <c r="G177" s="3"/>
       <c r="H177" s="3"/>
@@ -7200,13 +7213,13 @@
         <v>174</v>
       </c>
       <c r="B178" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C178" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="C178" s="3" t="s">
+      <c r="D178" s="3" t="s">
         <v>574</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>575</v>
       </c>
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
@@ -7219,19 +7232,19 @@
         <v>175</v>
       </c>
       <c r="B179" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C179" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="C179" s="3" t="s">
+      <c r="D179" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="D179" s="3" t="s">
+      <c r="E179" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F179" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="E179" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>579</v>
       </c>
       <c r="G179" s="3"/>
       <c r="H179" s="3"/>
@@ -7242,16 +7255,16 @@
         <v>176</v>
       </c>
       <c r="B180" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C180" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="C180" s="3" t="s">
+      <c r="D180" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="D180" s="3" t="s">
-        <v>582</v>
-      </c>
       <c r="E180" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3"/>
@@ -7263,13 +7276,13 @@
         <v>177</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C181" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="C181" s="3" t="s">
-        <v>584</v>
-      </c>
       <c r="D181" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
@@ -7282,13 +7295,13 @@
         <v>178</v>
       </c>
       <c r="B182" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C182" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="C182" s="3" t="s">
-        <v>586</v>
-      </c>
       <c r="D182" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
@@ -7301,22 +7314,22 @@
         <v>179</v>
       </c>
       <c r="B183" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C183" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="C183" s="3" t="s">
+      <c r="D183" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E183" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="D183" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E183" s="3" t="s">
+      <c r="F183" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="F183" s="3" t="s">
+      <c r="G183" s="3" t="s">
         <v>590</v>
-      </c>
-      <c r="G183" s="3" t="s">
-        <v>591</v>
       </c>
       <c r="H183" s="3"/>
       <c r="I183" s="3"/>
@@ -7326,13 +7339,13 @@
         <v>180</v>
       </c>
       <c r="B184" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C184" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="C184" s="3" t="s">
-        <v>593</v>
-      </c>
       <c r="D184" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
@@ -7345,13 +7358,13 @@
         <v>181</v>
       </c>
       <c r="B185" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C185" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="C185" s="3" t="s">
-        <v>595</v>
-      </c>
       <c r="D185" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
@@ -7364,13 +7377,13 @@
         <v>182</v>
       </c>
       <c r="B186" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C186" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="C186" s="3" t="s">
-        <v>597</v>
-      </c>
       <c r="D186" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
@@ -7383,13 +7396,13 @@
         <v>183</v>
       </c>
       <c r="B187" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C187" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="C187" s="3" t="s">
-        <v>599</v>
-      </c>
       <c r="D187" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
@@ -7402,13 +7415,13 @@
         <v>184</v>
       </c>
       <c r="B188" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C188" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="C188" s="3" t="s">
-        <v>601</v>
-      </c>
       <c r="D188" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
@@ -7421,13 +7434,13 @@
         <v>185</v>
       </c>
       <c r="B189" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C189" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="C189" s="3" t="s">
-        <v>603</v>
-      </c>
       <c r="D189" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
@@ -7440,10 +7453,10 @@
         <v>186</v>
       </c>
       <c r="B190" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C190" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="C190" s="3" t="s">
-        <v>605</v>
       </c>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -7457,19 +7470,19 @@
         <v>187</v>
       </c>
       <c r="B191" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C191" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="D191" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E191" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="D191" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>608</v>
-      </c>
       <c r="F191" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G191" s="3"/>
       <c r="H191" s="3"/>
@@ -7480,25 +7493,25 @@
         <v>188</v>
       </c>
       <c r="B192" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C192" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="C192" s="3" t="s">
+      <c r="D192" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="F192" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="D192" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F192" s="3" t="s">
-        <v>611</v>
-      </c>
       <c r="G192" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I192" s="3"/>
     </row>
@@ -7507,25 +7520,25 @@
         <v>189</v>
       </c>
       <c r="B193" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C193" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="C193" s="3" t="s">
-        <v>613</v>
-      </c>
       <c r="D193" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I193" s="3"/>
     </row>
@@ -7534,25 +7547,25 @@
         <v>190</v>
       </c>
       <c r="B194" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C194" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="C194" s="3" t="s">
-        <v>615</v>
-      </c>
       <c r="D194" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I194" s="3"/>
     </row>
@@ -7561,22 +7574,22 @@
         <v>191</v>
       </c>
       <c r="B195" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C195" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="C195" s="3" t="s">
+      <c r="D195" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="F195" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="D195" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>618</v>
-      </c>
       <c r="G195" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H195" s="3"/>
       <c r="I195" s="3"/>
@@ -7586,22 +7599,22 @@
         <v>192</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C196" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="C196" s="3" t="s">
-        <v>620</v>
-      </c>
       <c r="D196" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H196" s="3"/>
       <c r="I196" s="3"/>
@@ -7611,22 +7624,22 @@
         <v>193</v>
       </c>
       <c r="B197" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C197" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="C197" s="3" t="s">
+      <c r="D197" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E197" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="D197" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>623</v>
-      </c>
       <c r="F197" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H197" s="3"/>
       <c r="I197" s="3"/>
@@ -7636,19 +7649,19 @@
         <v>194</v>
       </c>
       <c r="B198" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C198" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="C198" s="3" t="s">
+      <c r="D198" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E198" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="D198" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E198" s="3" t="s">
-        <v>626</v>
-      </c>
       <c r="F198" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G198" s="3"/>
       <c r="H198" s="3"/>
@@ -7659,19 +7672,19 @@
         <v>195</v>
       </c>
       <c r="B199" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C199" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="C199" s="3" t="s">
-        <v>628</v>
-      </c>
       <c r="D199" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G199" s="3"/>
       <c r="H199" s="3"/>
@@ -7682,19 +7695,19 @@
         <v>196</v>
       </c>
       <c r="B200" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C200" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="C200" s="3" t="s">
-        <v>630</v>
-      </c>
       <c r="D200" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G200" s="3"/>
       <c r="H200" s="3"/>
@@ -7705,16 +7718,16 @@
         <v>197</v>
       </c>
       <c r="B201" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C201" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="C201" s="3" t="s">
-        <v>632</v>
-      </c>
       <c r="D201" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3"/>
@@ -7726,16 +7739,16 @@
         <v>198</v>
       </c>
       <c r="B202" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C202" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="C202" s="3" t="s">
-        <v>634</v>
-      </c>
       <c r="D202" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3"/>
@@ -7747,16 +7760,16 @@
         <v>199</v>
       </c>
       <c r="B203" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C203" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="C203" s="3" t="s">
-        <v>636</v>
-      </c>
       <c r="D203" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3"/>
@@ -7768,16 +7781,16 @@
         <v>200</v>
       </c>
       <c r="B204" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="C204" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="C204" s="3" t="s">
+      <c r="D204" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E204" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E204" s="3" t="s">
-        <v>639</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3"/>
@@ -7789,13 +7802,13 @@
         <v>201</v>
       </c>
       <c r="B205" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C205" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="C205" s="3" t="s">
+      <c r="D205" s="3" t="s">
         <v>641</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>642</v>
       </c>
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
@@ -7808,28 +7821,28 @@
         <v>202</v>
       </c>
       <c r="B206" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="C206" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="C206" s="3" t="s">
+      <c r="D206" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="D206" s="3" t="s">
+      <c r="E206" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="E206" s="3" t="s">
+      <c r="F206" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="F206" s="3" t="s">
+      <c r="G206" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="G206" s="3" t="s">
+      <c r="H206" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="H206" s="3" t="s">
+      <c r="I206" s="3" t="s">
         <v>649</v>
-      </c>
-      <c r="I206" s="3" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="207" spans="1:9" ht="56" x14ac:dyDescent="0.25">
@@ -7837,19 +7850,19 @@
         <v>203</v>
       </c>
       <c r="B207" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="C207" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="C207" s="3" t="s">
+      <c r="D207" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E207" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="D207" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E207" s="3" t="s">
+      <c r="F207" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="F207" s="3" t="s">
-        <v>654</v>
       </c>
       <c r="G207" s="3"/>
       <c r="H207" s="3"/>
@@ -7860,19 +7873,19 @@
         <v>204</v>
       </c>
       <c r="B208" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="C208" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="C208" s="3" t="s">
-        <v>656</v>
-      </c>
       <c r="D208" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E208" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="F208" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="F208" s="3" t="s">
-        <v>654</v>
       </c>
       <c r="G208" s="3"/>
       <c r="H208" s="3"/>
@@ -7883,13 +7896,13 @@
         <v>205</v>
       </c>
       <c r="B209" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C209" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="C209" s="3" t="s">
+      <c r="D209" s="3" t="s">
         <v>658</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>659</v>
       </c>
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
@@ -7902,16 +7915,16 @@
         <v>206</v>
       </c>
       <c r="B210" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="C210" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="C210" s="3" t="s">
+      <c r="D210" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="D210" s="3" t="s">
+      <c r="E210" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>663</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
@@ -7923,13 +7936,13 @@
         <v>207</v>
       </c>
       <c r="B211" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C211" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="C211" s="3" t="s">
+      <c r="D211" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>666</v>
       </c>
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
@@ -7942,22 +7955,22 @@
         <v>208</v>
       </c>
       <c r="B212" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="C212" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="C212" s="3" t="s">
+      <c r="D212" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="D212" s="3" t="s">
+      <c r="E212" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="E212" s="3" t="s">
+      <c r="F212" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="F212" s="3" t="s">
+      <c r="G212" s="3" t="s">
         <v>671</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>672</v>
       </c>
       <c r="H212" s="3"/>
       <c r="I212" s="3"/>
@@ -7967,19 +7980,19 @@
         <v>209</v>
       </c>
       <c r="B213" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="C213" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="C213" s="3" t="s">
+      <c r="D213" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="F213" s="3" t="s">
         <v>674</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>675</v>
       </c>
       <c r="G213" s="3"/>
       <c r="H213" s="3"/>
@@ -7990,19 +8003,19 @@
         <v>210</v>
       </c>
       <c r="B214" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C214" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="C214" s="3" t="s">
+      <c r="D214" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="E214" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="D214" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="E214" s="3" t="s">
+      <c r="F214" s="3" t="s">
         <v>678</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>679</v>
       </c>
       <c r="G214" s="3"/>
       <c r="H214" s="3"/>
@@ -8013,13 +8026,13 @@
         <v>211</v>
       </c>
       <c r="B215" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="C215" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="C215" s="3" t="s">
-        <v>681</v>
-      </c>
       <c r="D215" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
@@ -8032,19 +8045,19 @@
         <v>212</v>
       </c>
       <c r="B216" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="C216" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="C216" s="3" t="s">
+      <c r="D216" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="D216" s="3" t="s">
+      <c r="E216" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="E216" s="3" t="s">
+      <c r="F216" s="3" t="s">
         <v>685</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>686</v>
       </c>
       <c r="G216" s="3"/>
       <c r="H216" s="3"/>
@@ -8055,13 +8068,13 @@
         <v>213</v>
       </c>
       <c r="B217" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="C217" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="C217" s="3" t="s">
+      <c r="D217" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>689</v>
       </c>
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
@@ -8074,13 +8087,13 @@
         <v>214</v>
       </c>
       <c r="B218" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="C218" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="C218" s="3" t="s">
-        <v>691</v>
-      </c>
       <c r="D218" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
@@ -8093,13 +8106,13 @@
         <v>215</v>
       </c>
       <c r="B219" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="C219" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="C219" s="3" t="s">
-        <v>693</v>
-      </c>
       <c r="D219" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
@@ -8112,25 +8125,25 @@
         <v>216</v>
       </c>
       <c r="B220" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C220" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="C220" s="3" t="s">
+      <c r="D220" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G220" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="D220" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F220" s="3" t="s">
+      <c r="H220" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="G220" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="H220" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="I220" s="3"/>
     </row>
@@ -8139,19 +8152,19 @@
         <v>217</v>
       </c>
       <c r="B221" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C221" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="C221" s="3" t="s">
+      <c r="D221" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="D221" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>699</v>
-      </c>
       <c r="F221" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G221" s="3"/>
       <c r="H221" s="3"/>
@@ -8162,13 +8175,13 @@
         <v>218</v>
       </c>
       <c r="B222" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C222" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="C222" s="3" t="s">
+      <c r="D222" s="3" t="s">
         <v>701</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>702</v>
       </c>
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
@@ -8181,10 +8194,10 @@
         <v>219</v>
       </c>
       <c r="B223" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="C223" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>704</v>
       </c>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -8198,22 +8211,22 @@
         <v>220</v>
       </c>
       <c r="B224" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="C224" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="C224" s="3" t="s">
+      <c r="D224" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G224" s="3" t="s">
         <v>706</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G224" s="3" t="s">
-        <v>707</v>
       </c>
       <c r="H224" s="3"/>
       <c r="I224" s="3"/>
@@ -8223,22 +8236,22 @@
         <v>221</v>
       </c>
       <c r="B225" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C225" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="C225" s="3" t="s">
+      <c r="D225" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G225" s="3" t="s">
         <v>709</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E225" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="F225" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G225" s="3" t="s">
-        <v>710</v>
       </c>
       <c r="H225" s="3"/>
       <c r="I225" s="3"/>
@@ -8248,19 +8261,19 @@
         <v>222</v>
       </c>
       <c r="B226" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C226" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="C226" s="3" t="s">
+      <c r="D226" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="D226" s="3" t="s">
+      <c r="E226" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="E226" s="3" t="s">
+      <c r="F226" s="3" t="s">
         <v>714</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>715</v>
       </c>
       <c r="G226" s="3"/>
       <c r="H226" s="3"/>
@@ -8271,22 +8284,22 @@
         <v>223</v>
       </c>
       <c r="B227" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C227" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="C227" s="3" t="s">
+      <c r="D227" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="D227" s="3" t="s">
+      <c r="E227" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F227" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="E227" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F227" s="3" t="s">
+      <c r="G227" s="3" t="s">
         <v>719</v>
-      </c>
-      <c r="G227" s="3" t="s">
-        <v>720</v>
       </c>
       <c r="H227" s="3"/>
       <c r="I227" s="3"/>
@@ -8296,16 +8309,16 @@
         <v>224</v>
       </c>
       <c r="B228" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C228" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="C228" s="3" t="s">
+      <c r="D228" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="E228" s="3" t="s">
         <v>722</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>723</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3"/>
@@ -8317,13 +8330,13 @@
         <v>225</v>
       </c>
       <c r="B229" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C229" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="C229" s="3" t="s">
-        <v>725</v>
-      </c>
       <c r="D229" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
@@ -8336,13 +8349,13 @@
         <v>226</v>
       </c>
       <c r="B230" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C230" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="C230" s="3" t="s">
-        <v>727</v>
-      </c>
       <c r="D230" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
@@ -8355,16 +8368,16 @@
         <v>227</v>
       </c>
       <c r="B231" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C231" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="C231" s="3" t="s">
+      <c r="D231" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E231" s="3" t="s">
         <v>729</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>730</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3"/>
@@ -8376,16 +8389,16 @@
         <v>228</v>
       </c>
       <c r="B232" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="C232" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="C232" s="3" t="s">
+      <c r="D232" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E232" s="3" t="s">
         <v>732</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="E232" s="3" t="s">
-        <v>733</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3"/>
@@ -8397,16 +8410,16 @@
         <v>229</v>
       </c>
       <c r="B233" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C233" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="C233" s="3" t="s">
-        <v>735</v>
-      </c>
       <c r="D233" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3"/>
@@ -8418,22 +8431,22 @@
         <v>230</v>
       </c>
       <c r="B234" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="C234" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="C234" s="3" t="s">
+      <c r="D234" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F234" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="D234" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="E234" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F234" s="3" t="s">
-        <v>738</v>
-      </c>
       <c r="G234" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H234" s="3"/>
       <c r="I234" s="3"/>
@@ -8443,13 +8456,13 @@
         <v>231</v>
       </c>
       <c r="B235" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C235" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="C235" s="3" t="s">
-        <v>740</v>
-      </c>
       <c r="D235" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
@@ -8462,22 +8475,22 @@
         <v>232</v>
       </c>
       <c r="B236" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="C236" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="C236" s="3" t="s">
+      <c r="D236" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="D236" s="3" t="s">
+      <c r="E236" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="E236" s="3" t="s">
+      <c r="F236" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="F236" s="3" t="s">
+      <c r="G236" s="3" t="s">
         <v>745</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>746</v>
       </c>
       <c r="H236" s="3"/>
       <c r="I236" s="3"/>
@@ -8487,22 +8500,22 @@
         <v>233</v>
       </c>
       <c r="B237" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C237" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="C237" s="3" t="s">
+      <c r="D237" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G237" s="3" t="s">
         <v>748</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="E237" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>749</v>
       </c>
       <c r="H237" s="3"/>
       <c r="I237" s="3"/>
@@ -8512,19 +8525,19 @@
         <v>234</v>
       </c>
       <c r="B238" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="C238" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="C238" s="3" t="s">
+      <c r="D238" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="D238" s="3" t="s">
-        <v>752</v>
-      </c>
       <c r="E238" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G238" s="3"/>
       <c r="H238" s="3"/>
@@ -8535,16 +8548,16 @@
         <v>235</v>
       </c>
       <c r="B239" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="C239" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="C239" s="3" t="s">
+      <c r="D239" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="E239" s="3" t="s">
         <v>754</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="E239" s="3" t="s">
-        <v>755</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3"/>
@@ -8556,13 +8569,13 @@
         <v>236</v>
       </c>
       <c r="B240" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="C240" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="C240" s="3" t="s">
-        <v>757</v>
-      </c>
       <c r="D240" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
@@ -8575,28 +8588,28 @@
         <v>237</v>
       </c>
       <c r="B241" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="C241" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="C241" s="3" t="s">
+      <c r="D241" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F241" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="D241" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E241" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F241" s="3" t="s">
+      <c r="G241" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="G241" s="3" t="s">
+      <c r="H241" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="H241" s="3" t="s">
-        <v>762</v>
-      </c>
       <c r="I241" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="242" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -8604,19 +8617,19 @@
         <v>238</v>
       </c>
       <c r="B242" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="C242" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="C242" s="3" t="s">
-        <v>764</v>
-      </c>
       <c r="D242" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E242" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="F242" s="3" t="s">
         <v>761</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>762</v>
       </c>
       <c r="G242" s="3"/>
       <c r="H242" s="3"/>
@@ -8627,25 +8640,25 @@
         <v>239</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="C243" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="C243" s="3" t="s">
+      <c r="D243" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="D243" s="3" t="s">
-        <v>767</v>
-      </c>
       <c r="E243" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="F243" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="F243" s="3" t="s">
-        <v>762</v>
-      </c>
       <c r="G243" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I243" s="3"/>
     </row>
@@ -8654,22 +8667,22 @@
         <v>240</v>
       </c>
       <c r="B244" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="C244" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="C244" s="3" t="s">
+      <c r="D244" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="D244" s="3" t="s">
+      <c r="E244" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="E244" s="3" t="s">
+      <c r="F244" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G244" s="3" t="s">
         <v>771</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G244" s="3" t="s">
-        <v>772</v>
       </c>
       <c r="H244" s="3"/>
       <c r="I244" s="3"/>
@@ -8679,13 +8692,13 @@
         <v>241</v>
       </c>
       <c r="B245" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="C245" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="C245" s="3" t="s">
-        <v>774</v>
-      </c>
       <c r="D245" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
@@ -8698,25 +8711,25 @@
         <v>242</v>
       </c>
       <c r="B246" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="C246" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="C246" s="3" t="s">
+      <c r="D246" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="D246" s="3" t="s">
+      <c r="E246" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="E246" s="3" t="s">
+      <c r="F246" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="F246" s="3" t="s">
+      <c r="G246" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="G246" s="3" t="s">
+      <c r="H246" s="3" t="s">
         <v>780</v>
-      </c>
-      <c r="H246" s="3" t="s">
-        <v>781</v>
       </c>
       <c r="I246" s="3"/>
     </row>
@@ -8725,25 +8738,25 @@
         <v>243</v>
       </c>
       <c r="B247" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="C247" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="C247" s="3" t="s">
+      <c r="D247" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="E247" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="D247" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E247" s="3" t="s">
+      <c r="F247" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="G247" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="F247" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="G247" s="3" t="s">
+      <c r="H247" s="3" t="s">
         <v>785</v>
-      </c>
-      <c r="H247" s="3" t="s">
-        <v>786</v>
       </c>
       <c r="I247" s="3"/>
     </row>
@@ -8752,16 +8765,16 @@
         <v>244</v>
       </c>
       <c r="B248" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="C248" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="C248" s="3" t="s">
+      <c r="D248" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="E248" s="3" t="s">
         <v>788</v>
-      </c>
-      <c r="D248" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E248" s="3" t="s">
-        <v>789</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3"/>
@@ -8773,19 +8786,19 @@
         <v>245</v>
       </c>
       <c r="B249" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="C249" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="C249" s="3" t="s">
+      <c r="D249" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="E249" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="D249" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="E249" s="3" t="s">
+      <c r="F249" s="3" t="s">
         <v>792</v>
-      </c>
-      <c r="F249" s="3" t="s">
-        <v>793</v>
       </c>
       <c r="G249" s="3"/>
       <c r="H249" s="3"/>
@@ -8796,22 +8809,22 @@
         <v>246</v>
       </c>
       <c r="B250" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="C250" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="C250" s="3" t="s">
+      <c r="D250" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="D250" s="3" t="s">
+      <c r="E250" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="E250" s="3" t="s">
+      <c r="F250" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="F250" s="3" t="s">
-        <v>798</v>
-      </c>
       <c r="G250" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H250" s="3"/>
       <c r="I250" s="3"/>
@@ -8821,25 +8834,25 @@
         <v>247</v>
       </c>
       <c r="B251" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="C251" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="C251" s="3" t="s">
+      <c r="D251" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F251" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="D251" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E251" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F251" s="3" t="s">
-        <v>801</v>
-      </c>
       <c r="G251" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H251" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="H251" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="I251" s="3"/>
     </row>
@@ -8848,22 +8861,22 @@
         <v>248</v>
       </c>
       <c r="B252" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="C252" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="C252" s="3" t="s">
+      <c r="D252" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="D252" s="3" t="s">
+      <c r="E252" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="E252" s="3" t="s">
+      <c r="F252" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="F252" s="3" t="s">
+      <c r="G252" s="3" t="s">
         <v>806</v>
-      </c>
-      <c r="G252" s="3" t="s">
-        <v>807</v>
       </c>
       <c r="H252" s="3"/>
       <c r="I252" s="3"/>
@@ -8873,22 +8886,22 @@
         <v>249</v>
       </c>
       <c r="B253" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="C253" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="C253" s="3" t="s">
+      <c r="D253" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="F253" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="D253" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="E253" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="F253" s="3" t="s">
+      <c r="G253" s="3" t="s">
         <v>810</v>
-      </c>
-      <c r="G253" s="3" t="s">
-        <v>811</v>
       </c>
       <c r="H253" s="3"/>
       <c r="I253" s="3"/>
@@ -8898,25 +8911,25 @@
         <v>250</v>
       </c>
       <c r="B254" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="C254" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="C254" s="3" t="s">
-        <v>813</v>
-      </c>
       <c r="D254" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F254" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="G254" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="G254" s="3" t="s">
+      <c r="H254" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="H254" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="I254" s="3"/>
     </row>
@@ -8925,19 +8938,19 @@
         <v>251</v>
       </c>
       <c r="B255" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="C255" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="C255" s="3" t="s">
+      <c r="D255" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F255" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E255" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>816</v>
       </c>
       <c r="G255" s="3"/>
       <c r="H255" s="3"/>
@@ -8948,16 +8961,16 @@
         <v>252</v>
       </c>
       <c r="B256" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="C256" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="C256" s="3" t="s">
-        <v>818</v>
-      </c>
       <c r="D256" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3"/>
@@ -8969,10 +8982,10 @@
         <v>253</v>
       </c>
       <c r="B257" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="C257" s="3" t="s">
         <v>819</v>
-      </c>
-      <c r="C257" s="3" t="s">
-        <v>820</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -8986,19 +8999,19 @@
         <v>254</v>
       </c>
       <c r="B258" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="C258" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="C258" s="3" t="s">
+      <c r="D258" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F258" s="3" t="s">
         <v>822</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>823</v>
       </c>
       <c r="G258" s="3"/>
       <c r="H258" s="3"/>
@@ -9009,16 +9022,16 @@
         <v>255</v>
       </c>
       <c r="B259" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="C259" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="C259" s="3" t="s">
+      <c r="D259" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E259" s="3" t="s">
         <v>825</v>
-      </c>
-      <c r="D259" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E259" s="3" t="s">
-        <v>826</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3"/>
@@ -9030,22 +9043,22 @@
         <v>256</v>
       </c>
       <c r="B260" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="C260" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="C260" s="3" t="s">
+      <c r="D260" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="F260" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="D260" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E260" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="F260" s="3" t="s">
+      <c r="G260" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="G260" s="3" t="s">
-        <v>830</v>
       </c>
       <c r="H260" s="3"/>
       <c r="I260" s="3"/>
@@ -9055,22 +9068,22 @@
         <v>257</v>
       </c>
       <c r="B261" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="C261" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="C261" s="3" t="s">
+      <c r="D261" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="D261" s="3" t="s">
-        <v>833</v>
-      </c>
       <c r="E261" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F261" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F261" s="3" t="s">
+      <c r="G261" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G261" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="H261" s="3"/>
       <c r="I261" s="3"/>
@@ -9080,19 +9093,19 @@
         <v>258</v>
       </c>
       <c r="B262" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="C262" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="C262" s="3" t="s">
-        <v>835</v>
-      </c>
       <c r="D262" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G262" s="3"/>
       <c r="H262" s="3"/>
@@ -9103,22 +9116,22 @@
         <v>259</v>
       </c>
       <c r="B263" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="C263" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="C263" s="3" t="s">
-        <v>837</v>
-      </c>
       <c r="D263" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H263" s="3"/>
       <c r="I263" s="3"/>
@@ -9128,25 +9141,25 @@
         <v>260</v>
       </c>
       <c r="B264" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="C264" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="C264" s="3" t="s">
+      <c r="D264" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G264" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="D264" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="E264" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F264" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G264" s="3" t="s">
+      <c r="H264" s="3" t="s">
         <v>840</v>
-      </c>
-      <c r="H264" s="3" t="s">
-        <v>841</v>
       </c>
       <c r="I264" s="3"/>
     </row>
@@ -9155,19 +9168,19 @@
         <v>261</v>
       </c>
       <c r="B265" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="C265" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="C265" s="3" t="s">
-        <v>843</v>
-      </c>
       <c r="D265" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G265" s="3"/>
       <c r="H265" s="3"/>
@@ -9178,22 +9191,22 @@
         <v>262</v>
       </c>
       <c r="B266" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="C266" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="C266" s="3" t="s">
-        <v>845</v>
-      </c>
       <c r="D266" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H266" s="3"/>
       <c r="I266" s="3"/>
@@ -9203,19 +9216,19 @@
         <v>263</v>
       </c>
       <c r="B267" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="C267" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="C267" s="3" t="s">
-        <v>847</v>
-      </c>
       <c r="D267" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G267" s="3"/>
       <c r="H267" s="3"/>
@@ -9226,22 +9239,22 @@
         <v>264</v>
       </c>
       <c r="B268" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="C268" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="C268" s="3" t="s">
+      <c r="D268" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="D268" s="3" t="s">
+      <c r="E268" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F268" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="E268" s="3" t="s">
+      <c r="G268" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="F268" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="G268" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="3"/>
@@ -9251,25 +9264,25 @@
         <v>265</v>
       </c>
       <c r="B269" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="C269" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="C269" s="3" t="s">
-        <v>853</v>
-      </c>
       <c r="D269" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F269" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="E269" s="3" t="s">
+      <c r="G269" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="F269" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="G269" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="H269" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I269" s="3"/>
     </row>
@@ -9278,19 +9291,19 @@
         <v>266</v>
       </c>
       <c r="B270" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="C270" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="C270" s="3" t="s">
-        <v>855</v>
-      </c>
       <c r="D270" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="F270" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="E270" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="F270" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="G270" s="3"/>
       <c r="H270" s="3"/>
@@ -9301,22 +9314,22 @@
         <v>267</v>
       </c>
       <c r="B271" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="C271" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="C271" s="3" t="s">
-        <v>857</v>
-      </c>
       <c r="D271" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H271" s="3"/>
       <c r="I271" s="3"/>
@@ -9326,19 +9339,19 @@
         <v>268</v>
       </c>
       <c r="B272" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="C272" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="C272" s="3" t="s">
-        <v>859</v>
-      </c>
       <c r="D272" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G272" s="3"/>
       <c r="H272" s="3"/>
@@ -9349,19 +9362,19 @@
         <v>269</v>
       </c>
       <c r="B273" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="C273" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="C273" s="3" t="s">
-        <v>861</v>
-      </c>
       <c r="D273" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G273" s="3"/>
       <c r="H273" s="3"/>
@@ -9372,28 +9385,28 @@
         <v>270</v>
       </c>
       <c r="B274" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="C274" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="C274" s="3" t="s">
+      <c r="D274" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G274" s="3" t="s">
         <v>863</v>
       </c>
-      <c r="D274" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E274" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F274" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G274" s="3" t="s">
+      <c r="H274" s="3" t="s">
         <v>864</v>
       </c>
-      <c r="H274" s="3" t="s">
+      <c r="I274" s="3" t="s">
         <v>865</v>
-      </c>
-      <c r="I274" s="3" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="275" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -9401,25 +9414,25 @@
         <v>271</v>
       </c>
       <c r="B275" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="C275" s="3" t="s">
         <v>867</v>
       </c>
-      <c r="C275" s="3" t="s">
+      <c r="D275" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="D275" s="3" t="s">
+      <c r="E275" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="G275" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="E275" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F275" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="G275" s="3" t="s">
-        <v>870</v>
-      </c>
       <c r="H275" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I275" s="3"/>
     </row>
@@ -9428,13 +9441,13 @@
         <v>272</v>
       </c>
       <c r="B276" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="C276" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="C276" s="3" t="s">
+      <c r="D276" s="3" t="s">
         <v>872</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>873</v>
       </c>
       <c r="E276" s="3"/>
       <c r="F276" s="3"/>
@@ -9447,16 +9460,16 @@
         <v>273</v>
       </c>
       <c r="B277" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="C277" s="3" t="s">
         <v>874</v>
       </c>
-      <c r="C277" s="3" t="s">
+      <c r="D277" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="D277" s="3" t="s">
-        <v>876</v>
-      </c>
       <c r="E277" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3"/>
@@ -9468,19 +9481,19 @@
         <v>274</v>
       </c>
       <c r="B278" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="C278" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="C278" s="3" t="s">
+      <c r="D278" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="D278" s="3" t="s">
+      <c r="E278" s="3" t="s">
         <v>879</v>
       </c>
-      <c r="E278" s="3" t="s">
+      <c r="F278" s="3" t="s">
         <v>880</v>
-      </c>
-      <c r="F278" s="3" t="s">
-        <v>881</v>
       </c>
       <c r="G278" s="3"/>
       <c r="H278" s="3"/>
@@ -9491,28 +9504,28 @@
         <v>275</v>
       </c>
       <c r="B279" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="C279" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="C279" s="3" t="s">
+      <c r="D279" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="D279" s="3" t="s">
+      <c r="E279" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="E279" s="3" t="s">
+      <c r="F279" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="F279" s="3" t="s">
+      <c r="G279" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="G279" s="3" t="s">
-        <v>887</v>
-      </c>
       <c r="H279" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I279" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="280" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -9520,22 +9533,22 @@
         <v>276</v>
       </c>
       <c r="B280" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="C280" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="C280" s="3" t="s">
+      <c r="D280" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="D280" s="3" t="s">
+      <c r="E280" s="3" t="s">
         <v>890</v>
       </c>
-      <c r="E280" s="3" t="s">
-        <v>891</v>
-      </c>
       <c r="F280" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H280" s="3"/>
       <c r="I280" s="3"/>
@@ -9545,22 +9558,22 @@
         <v>277</v>
       </c>
       <c r="B281" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="C281" s="3" t="s">
         <v>892</v>
       </c>
-      <c r="C281" s="3" t="s">
+      <c r="D281" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="D281" s="3" t="s">
+      <c r="E281" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="F281" s="3" t="s">
         <v>894</v>
       </c>
-      <c r="E281" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="F281" s="3" t="s">
+      <c r="G281" s="3" t="s">
         <v>895</v>
-      </c>
-      <c r="G281" s="3" t="s">
-        <v>896</v>
       </c>
       <c r="H281" s="3"/>
       <c r="I281" s="3"/>
@@ -9570,22 +9583,22 @@
         <v>278</v>
       </c>
       <c r="B282" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="C282" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="C282" s="3" t="s">
+      <c r="D282" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E282" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="D282" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E282" s="3" t="s">
+      <c r="F282" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="F282" s="3" t="s">
-        <v>900</v>
-      </c>
       <c r="G282" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H282" s="3"/>
       <c r="I282" s="3"/>
@@ -9595,28 +9608,28 @@
         <v>279</v>
       </c>
       <c r="B283" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="C283" s="3" t="s">
         <v>901</v>
       </c>
-      <c r="C283" s="3" t="s">
+      <c r="D283" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E283" s="3" t="s">
         <v>902</v>
       </c>
-      <c r="D283" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E283" s="3" t="s">
+      <c r="F283" s="3" t="s">
         <v>903</v>
       </c>
-      <c r="F283" s="3" t="s">
+      <c r="G283" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="G283" s="3" t="s">
+      <c r="H283" s="3" t="s">
         <v>905</v>
       </c>
-      <c r="H283" s="3" t="s">
-        <v>906</v>
-      </c>
       <c r="I283" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="284" spans="1:9" ht="56" x14ac:dyDescent="0.25">
@@ -9624,22 +9637,22 @@
         <v>280</v>
       </c>
       <c r="B284" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="C284" s="3" t="s">
         <v>907</v>
       </c>
-      <c r="C284" s="3" t="s">
+      <c r="D284" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F284" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="D284" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="E284" s="3" t="s">
+      <c r="G284" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F284" s="3" t="s">
-        <v>909</v>
-      </c>
-      <c r="G284" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="H284" s="3"/>
       <c r="I284" s="3"/>
@@ -9649,28 +9662,28 @@
         <v>281</v>
       </c>
       <c r="B285" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C285" s="3" t="s">
         <v>910</v>
       </c>
-      <c r="C285" s="3" t="s">
-        <v>911</v>
-      </c>
       <c r="D285" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="E285" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="E285" s="3" t="s">
+      <c r="F285" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="F285" s="3" t="s">
+      <c r="G285" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="G285" s="3" t="s">
-        <v>746</v>
-      </c>
       <c r="H285" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="I285" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="286" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -9678,19 +9691,19 @@
         <v>282</v>
       </c>
       <c r="B286" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C286" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="C286" s="3" t="s">
+      <c r="D286" s="3" t="s">
         <v>913</v>
       </c>
-      <c r="D286" s="3" t="s">
+      <c r="E286" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="E286" s="3" t="s">
+      <c r="F286" s="3" t="s">
         <v>915</v>
-      </c>
-      <c r="F286" s="3" t="s">
-        <v>916</v>
       </c>
       <c r="G286" s="3"/>
       <c r="H286" s="3"/>
@@ -9701,16 +9714,16 @@
         <v>283</v>
       </c>
       <c r="B287" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="C287" s="3" t="s">
         <v>917</v>
       </c>
-      <c r="C287" s="3" t="s">
+      <c r="D287" s="3" t="s">
         <v>918</v>
       </c>
-      <c r="D287" s="3" t="s">
-        <v>919</v>
-      </c>
       <c r="E287" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3"/>
@@ -9722,13 +9735,13 @@
         <v>284</v>
       </c>
       <c r="B288" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="C288" s="3" t="s">
         <v>920</v>
       </c>
-      <c r="C288" s="3" t="s">
-        <v>921</v>
-      </c>
       <c r="D288" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E288" s="3"/>
       <c r="F288" s="3"/>
@@ -9741,22 +9754,22 @@
         <v>285</v>
       </c>
       <c r="B289" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="C289" s="3" t="s">
         <v>922</v>
       </c>
-      <c r="C289" s="3" t="s">
+      <c r="D289" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="E289" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D289" s="3" t="s">
-        <v>894</v>
-      </c>
-      <c r="E289" s="3" t="s">
+      <c r="F289" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="G289" s="3" t="s">
         <v>924</v>
-      </c>
-      <c r="F289" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="G289" s="3" t="s">
-        <v>925</v>
       </c>
       <c r="H289" s="3"/>
       <c r="I289" s="3"/>
@@ -9766,22 +9779,22 @@
         <v>286</v>
       </c>
       <c r="B290" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="C290" s="3" t="s">
         <v>926</v>
       </c>
-      <c r="C290" s="3" t="s">
+      <c r="D290" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="E290" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F290" s="3" t="s">
         <v>927</v>
       </c>
-      <c r="D290" s="3" t="s">
-        <v>914</v>
-      </c>
-      <c r="E290" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F290" s="3" t="s">
+      <c r="G290" s="3" t="s">
         <v>928</v>
-      </c>
-      <c r="G290" s="3" t="s">
-        <v>929</v>
       </c>
       <c r="H290" s="3"/>
       <c r="I290" s="3"/>
@@ -9791,16 +9804,16 @@
         <v>287</v>
       </c>
       <c r="B291" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="C291" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="C291" s="3" t="s">
-        <v>931</v>
-      </c>
       <c r="D291" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3"/>
@@ -9812,22 +9825,22 @@
         <v>288</v>
       </c>
       <c r="B292" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="C292" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="C292" s="3" t="s">
-        <v>933</v>
-      </c>
       <c r="D292" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E292" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F292" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F292" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="G292" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H292" s="3"/>
       <c r="I292" s="3"/>
@@ -9837,22 +9850,22 @@
         <v>289</v>
       </c>
       <c r="B293" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="C293" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="C293" s="3" t="s">
-        <v>935</v>
-      </c>
       <c r="D293" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="E293" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="E293" s="3" t="s">
+      <c r="F293" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="F293" s="3" t="s">
-        <v>916</v>
-      </c>
       <c r="G293" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H293" s="3"/>
       <c r="I293" s="3"/>
@@ -9862,16 +9875,16 @@
         <v>290</v>
       </c>
       <c r="B294" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="C294" s="3" t="s">
         <v>936</v>
       </c>
-      <c r="C294" s="3" t="s">
-        <v>937</v>
-      </c>
       <c r="D294" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3"/>
@@ -9883,13 +9896,13 @@
         <v>291</v>
       </c>
       <c r="B295" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="C295" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="C295" s="3" t="s">
-        <v>939</v>
-      </c>
       <c r="D295" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E295" s="3"/>
       <c r="F295" s="3"/>
@@ -9902,19 +9915,19 @@
         <v>292</v>
       </c>
       <c r="B296" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="C296" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="C296" s="3" t="s">
-        <v>941</v>
-      </c>
       <c r="D296" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E296" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E296" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="F296" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
@@ -9925,16 +9938,16 @@
         <v>293</v>
       </c>
       <c r="B297" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="C297" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="C297" s="3" t="s">
-        <v>943</v>
-      </c>
       <c r="D297" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3"/>
@@ -9946,13 +9959,13 @@
         <v>294</v>
       </c>
       <c r="B298" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C298" s="3" t="s">
         <v>944</v>
       </c>
-      <c r="C298" s="3" t="s">
-        <v>945</v>
-      </c>
       <c r="D298" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E298" s="3"/>
       <c r="F298" s="3"/>
@@ -9965,25 +9978,25 @@
         <v>295</v>
       </c>
       <c r="B299" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="C299" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="C299" s="3" t="s">
+      <c r="D299" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G299" s="3" t="s">
         <v>947</v>
       </c>
-      <c r="D299" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E299" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F299" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G299" s="3" t="s">
+      <c r="H299" s="3" t="s">
         <v>948</v>
-      </c>
-      <c r="H299" s="3" t="s">
-        <v>949</v>
       </c>
       <c r="I299" s="3"/>
     </row>
@@ -9992,25 +10005,25 @@
         <v>296</v>
       </c>
       <c r="B300" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="C300" s="3" t="s">
         <v>950</v>
       </c>
-      <c r="C300" s="3" t="s">
-        <v>951</v>
-      </c>
       <c r="D300" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E300" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F300" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F300" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="G300" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="H300" s="3" t="s">
         <v>948</v>
-      </c>
-      <c r="H300" s="3" t="s">
-        <v>949</v>
       </c>
       <c r="I300" s="3"/>
     </row>
@@ -10019,22 +10032,22 @@
         <v>297</v>
       </c>
       <c r="B301" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="C301" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="C301" s="3" t="s">
-        <v>953</v>
-      </c>
       <c r="D301" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F301" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H301" s="3"/>
       <c r="I301" s="3"/>
@@ -10044,25 +10057,25 @@
         <v>298</v>
       </c>
       <c r="B302" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="C302" s="3" t="s">
         <v>954</v>
       </c>
-      <c r="C302" s="3" t="s">
+      <c r="D302" s="3" t="s">
         <v>955</v>
       </c>
-      <c r="D302" s="3" t="s">
+      <c r="E302" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F302" s="3" t="s">
         <v>956</v>
       </c>
-      <c r="E302" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F302" s="3" t="s">
+      <c r="G302" s="3" t="s">
         <v>957</v>
       </c>
-      <c r="G302" s="3" t="s">
-        <v>958</v>
-      </c>
       <c r="H302" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I302" s="3"/>
     </row>
@@ -10071,25 +10084,25 @@
         <v>299</v>
       </c>
       <c r="B303" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="C303" s="3" t="s">
         <v>959</v>
       </c>
-      <c r="C303" s="3" t="s">
+      <c r="D303" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E303" s="3" t="s">
         <v>960</v>
       </c>
-      <c r="D303" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E303" s="3" t="s">
+      <c r="F303" s="3" t="s">
         <v>961</v>
       </c>
-      <c r="F303" s="3" t="s">
+      <c r="G303" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H303" s="3" t="s">
         <v>962</v>
-      </c>
-      <c r="G303" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H303" s="3" t="s">
-        <v>963</v>
       </c>
       <c r="I303" s="3"/>
     </row>
@@ -10098,16 +10111,16 @@
         <v>300</v>
       </c>
       <c r="B304" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="C304" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="C304" s="3" t="s">
+      <c r="D304" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E304" s="3" t="s">
         <v>965</v>
-      </c>
-      <c r="D304" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E304" s="3" t="s">
-        <v>966</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3"/>
@@ -10119,25 +10132,25 @@
         <v>301</v>
       </c>
       <c r="B305" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C305" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="C305" s="3" t="s">
+      <c r="D305" s="3" t="s">
         <v>968</v>
       </c>
-      <c r="D305" s="3" t="s">
+      <c r="E305" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="F305" s="3" t="s">
         <v>969</v>
       </c>
-      <c r="E305" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="F305" s="3" t="s">
+      <c r="G305" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="G305" s="3" t="s">
+      <c r="H305" s="3" t="s">
         <v>971</v>
-      </c>
-      <c r="H305" s="3" t="s">
-        <v>972</v>
       </c>
       <c r="I305" s="3"/>
     </row>
@@ -10146,22 +10159,22 @@
         <v>302</v>
       </c>
       <c r="B306" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="C306" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="C306" s="3" t="s">
+      <c r="D306" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="F306" s="3" t="s">
         <v>974</v>
       </c>
-      <c r="D306" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E306" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F306" s="3" t="s">
+      <c r="G306" s="3" t="s">
         <v>975</v>
-      </c>
-      <c r="G306" s="3" t="s">
-        <v>976</v>
       </c>
       <c r="H306" s="3"/>
       <c r="I306" s="3"/>
@@ -10171,25 +10184,25 @@
         <v>303</v>
       </c>
       <c r="B307" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="C307" s="3" t="s">
         <v>977</v>
       </c>
-      <c r="C307" s="3" t="s">
+      <c r="D307" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="F307" s="3" t="s">
         <v>978</v>
       </c>
-      <c r="D307" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="E307" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F307" s="3" t="s">
+      <c r="G307" s="3" t="s">
         <v>979</v>
       </c>
-      <c r="G307" s="3" t="s">
-        <v>980</v>
-      </c>
       <c r="H307" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="I307" s="3"/>
     </row>
@@ -10198,25 +10211,25 @@
         <v>304</v>
       </c>
       <c r="B308" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C308" s="3" t="s">
         <v>981</v>
       </c>
-      <c r="C308" s="3" t="s">
-        <v>982</v>
-      </c>
       <c r="D308" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F308" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="G308" s="3" t="s">
         <v>979</v>
       </c>
-      <c r="G308" s="3" t="s">
-        <v>980</v>
-      </c>
       <c r="H308" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I308" s="3"/>
     </row>
@@ -10225,16 +10238,16 @@
         <v>305</v>
       </c>
       <c r="B309" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="C309" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="C309" s="3" t="s">
+      <c r="D309" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="D309" s="3" t="s">
+      <c r="E309" s="3" t="s">
         <v>985</v>
-      </c>
-      <c r="E309" s="3" t="s">
-        <v>986</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3"/>
@@ -10246,13 +10259,13 @@
         <v>306</v>
       </c>
       <c r="B310" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="C310" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="C310" s="3" t="s">
-        <v>988</v>
-      </c>
       <c r="D310" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E310" s="3"/>
       <c r="F310" s="3"/>
@@ -10265,22 +10278,22 @@
         <v>307</v>
       </c>
       <c r="B311" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="C311" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="C311" s="3" t="s">
+      <c r="D311" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E311" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="D311" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E311" s="3" t="s">
-        <v>991</v>
-      </c>
       <c r="F311" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G311" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H311" s="3"/>
       <c r="I311" s="3"/>
@@ -10290,16 +10303,16 @@
         <v>308</v>
       </c>
       <c r="B312" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C312" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="C312" s="3" t="s">
+      <c r="D312" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E312" s="3" t="s">
         <v>993</v>
-      </c>
-      <c r="D312" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E312" s="3" t="s">
-        <v>994</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3"/>
@@ -10311,19 +10324,19 @@
         <v>309</v>
       </c>
       <c r="B313" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="C313" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="C313" s="3" t="s">
+      <c r="D313" s="3" t="s">
         <v>996</v>
       </c>
-      <c r="D313" s="3" t="s">
+      <c r="E313" s="3" t="s">
         <v>997</v>
       </c>
-      <c r="E313" s="3" t="s">
+      <c r="F313" s="3" t="s">
         <v>998</v>
-      </c>
-      <c r="F313" s="3" t="s">
-        <v>999</v>
       </c>
       <c r="G313" s="3"/>
       <c r="H313" s="3"/>
@@ -10334,28 +10347,28 @@
         <v>310</v>
       </c>
       <c r="B314" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="C314" s="3" t="s">
         <v>1000</v>
       </c>
-      <c r="C314" s="3" t="s">
+      <c r="D314" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E314" s="3" t="s">
         <v>1001</v>
       </c>
-      <c r="D314" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E314" s="3" t="s">
+      <c r="F314" s="3" t="s">
         <v>1002</v>
       </c>
-      <c r="F314" s="3" t="s">
+      <c r="G314" s="3" t="s">
         <v>1003</v>
       </c>
-      <c r="G314" s="3" t="s">
+      <c r="H314" s="3" t="s">
         <v>1004</v>
       </c>
-      <c r="H314" s="3" t="s">
-        <v>1005</v>
-      </c>
       <c r="I314" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="315" spans="1:9" ht="56" x14ac:dyDescent="0.25">
@@ -10363,28 +10376,28 @@
         <v>311</v>
       </c>
       <c r="B315" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C315" s="3" t="s">
         <v>1006</v>
       </c>
-      <c r="C315" s="3" t="s">
+      <c r="D315" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G315" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="D315" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E315" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="F315" s="3" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G315" s="3" t="s">
-        <v>1008</v>
-      </c>
       <c r="H315" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I315" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
